--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/COLORADO_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/COLORADO_2018.xlsx
@@ -1453,7 +1453,7 @@
         <v>15</v>
       </c>
       <c r="D61">
-        <v>0.0009807767752059631</v>
+        <v>0.0009807767752059633</v>
       </c>
     </row>
     <row r="62">
@@ -1633,7 +1633,7 @@
         <v>15</v>
       </c>
       <c r="D71">
-        <v>0.0009807767752059631</v>
+        <v>0.0009807767752059633</v>
       </c>
     </row>
     <row r="72">
@@ -1921,7 +1921,7 @@
         <v>15</v>
       </c>
       <c r="D87">
-        <v>0.0009807767752059631</v>
+        <v>0.0009807767752059633</v>
       </c>
     </row>
     <row r="88">
@@ -1957,7 +1957,7 @@
         <v>14</v>
       </c>
       <c r="D89">
-        <v>0.0009153916568588989</v>
+        <v>0.0009153916568588988</v>
       </c>
     </row>
     <row r="90">
@@ -2605,7 +2605,7 @@
         <v>14</v>
       </c>
       <c r="D125">
-        <v>0.0009153916568588989</v>
+        <v>0.0009153916568588988</v>
       </c>
     </row>
     <row r="126">
@@ -2641,7 +2641,7 @@
         <v>15</v>
       </c>
       <c r="D127">
-        <v>0.0009807767752059631</v>
+        <v>0.0009807767752059633</v>
       </c>
     </row>
     <row r="128">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C138">
@@ -2875,7 +2875,7 @@
         <v>15</v>
       </c>
       <c r="D140">
-        <v>0.0009807767752059631</v>
+        <v>0.0009807767752059633</v>
       </c>
     </row>
     <row r="141">
@@ -3595,7 +3595,7 @@
         <v>14</v>
       </c>
       <c r="D180">
-        <v>0.0009153916568588989</v>
+        <v>0.0009153916568588988</v>
       </c>
     </row>
     <row r="181">
@@ -3685,7 +3685,7 @@
         <v>15</v>
       </c>
       <c r="D185">
-        <v>0.0009807767752059631</v>
+        <v>0.0009807767752059633</v>
       </c>
     </row>
     <row r="186">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C190">
@@ -3901,7 +3901,7 @@
         <v>15</v>
       </c>
       <c r="D197">
-        <v>0.0009807767752059631</v>
+        <v>0.0009807767752059633</v>
       </c>
     </row>
     <row r="198">
@@ -4063,7 +4063,7 @@
         <v>14</v>
       </c>
       <c r="D206">
-        <v>0.0009153916568588989</v>
+        <v>0.0009153916568588988</v>
       </c>
     </row>
     <row r="207">
@@ -5071,7 +5071,7 @@
         <v>14</v>
       </c>
       <c r="D262">
-        <v>0.0009153916568588989</v>
+        <v>0.0009153916568588988</v>
       </c>
     </row>
     <row r="263">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C311">
@@ -6133,7 +6133,7 @@
         <v>15</v>
       </c>
       <c r="D321">
-        <v>0.0009807767752059631</v>
+        <v>0.0009807767752059633</v>
       </c>
     </row>
     <row r="322">
@@ -6277,7 +6277,7 @@
         <v>15</v>
       </c>
       <c r="D329">
-        <v>0.0009807767752059631</v>
+        <v>0.0009807767752059633</v>
       </c>
     </row>
     <row r="330">
@@ -6457,7 +6457,7 @@
         <v>15</v>
       </c>
       <c r="D339">
-        <v>0.0009807767752059631</v>
+        <v>0.0009807767752059633</v>
       </c>
     </row>
     <row r="340">
@@ -6583,7 +6583,7 @@
         <v>15</v>
       </c>
       <c r="D346">
-        <v>0.0009807767752059631</v>
+        <v>0.0009807767752059633</v>
       </c>
     </row>
     <row r="347">
@@ -8239,7 +8239,7 @@
         <v>14</v>
       </c>
       <c r="D438">
-        <v>0.0009153916568588989</v>
+        <v>0.0009153916568588988</v>
       </c>
     </row>
     <row r="439">
@@ -9283,7 +9283,7 @@
         <v>14</v>
       </c>
       <c r="D496">
-        <v>0.0009153916568588989</v>
+        <v>0.0009153916568588988</v>
       </c>
     </row>
     <row r="497">
@@ -9877,7 +9877,7 @@
         <v>15</v>
       </c>
       <c r="D529">
-        <v>0.0009807767752059631</v>
+        <v>0.0009807767752059633</v>
       </c>
     </row>
     <row r="530">
@@ -9949,7 +9949,7 @@
         <v>14</v>
       </c>
       <c r="D533">
-        <v>0.0009153916568588989</v>
+        <v>0.0009153916568588988</v>
       </c>
     </row>
     <row r="534">
@@ -11317,7 +11317,7 @@
         <v>15</v>
       </c>
       <c r="D609">
-        <v>0.0009807767752059631</v>
+        <v>0.0009807767752059633</v>
       </c>
     </row>
     <row r="610">
@@ -11947,7 +11947,7 @@
         <v>14</v>
       </c>
       <c r="D644">
-        <v>0.0009153916568588989</v>
+        <v>0.0009153916568588988</v>
       </c>
     </row>
     <row r="645">
@@ -13801,7 +13801,7 @@
         <v>14</v>
       </c>
       <c r="D747">
-        <v>0.0009153916568588989</v>
+        <v>0.0009153916568588988</v>
       </c>
     </row>
     <row r="748">
@@ -13938,7 +13938,7 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C755">
@@ -14280,7 +14280,7 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C774">
@@ -17005,7 +17005,7 @@
         <v>15</v>
       </c>
       <c r="D925">
-        <v>0.0009807767752059631</v>
+        <v>0.0009807767752059633</v>
       </c>
     </row>
     <row r="926">
@@ -17725,7 +17725,7 @@
         <v>14</v>
       </c>
       <c r="D965">
-        <v>0.0009153916568588989</v>
+        <v>0.0009153916568588988</v>
       </c>
     </row>
     <row r="966">
@@ -17779,7 +17779,7 @@
         <v>15</v>
       </c>
       <c r="D968">
-        <v>0.0009807767752059631</v>
+        <v>0.0009807767752059633</v>
       </c>
     </row>
     <row r="969">
@@ -17977,7 +17977,7 @@
         <v>15</v>
       </c>
       <c r="D979">
-        <v>0.0009807767752059631</v>
+        <v>0.0009807767752059633</v>
       </c>
     </row>
     <row r="980">
@@ -18445,7 +18445,7 @@
         <v>15</v>
       </c>
       <c r="D1005">
-        <v>0.0009807767752059631</v>
+        <v>0.0009807767752059633</v>
       </c>
     </row>
     <row r="1006">
@@ -18553,7 +18553,7 @@
         <v>14</v>
       </c>
       <c r="D1011">
-        <v>0.0009153916568588989</v>
+        <v>0.0009153916568588988</v>
       </c>
     </row>
     <row r="1012">
@@ -18913,7 +18913,7 @@
         <v>15</v>
       </c>
       <c r="D1031">
-        <v>0.0009807767752059631</v>
+        <v>0.0009807767752059633</v>
       </c>
     </row>
     <row r="1032">
@@ -20965,7 +20965,7 @@
         <v>14</v>
       </c>
       <c r="D1145">
-        <v>0.0009153916568588989</v>
+        <v>0.0009153916568588988</v>
       </c>
     </row>
     <row r="1146">
@@ -21253,7 +21253,7 @@
         <v>15</v>
       </c>
       <c r="D1161">
-        <v>0.0009807767752059631</v>
+        <v>0.0009807767752059633</v>
       </c>
     </row>
     <row r="1162">
